--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_355_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_355_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>7</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1923,7 +1923,7 @@
         <v>35</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2315,16 +2315,16 @@
         <v>43</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X22" t="n">
         <v>10</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>136</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>33</v>
@@ -4292,16 +4292,16 @@
         <v>24</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>2</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5863,13 +5863,13 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" t="n">
         <v>8</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6255,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
         <v>3</v>
@@ -6784,16 +6784,16 @@
         <v>92</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X48" t="n">
         <v>23</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_355_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_355_EL.xlsx
@@ -674,10 +674,10 @@
         <v>7</v>
       </c>
       <c r="N2" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
         <v>4</v>
@@ -692,20 +692,20 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.62</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="P3" t="n">
         <v>7</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>74.19</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -2327,14 +2327,14 @@
         <v>2</v>
       </c>
       <c r="X22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y27" t="n">
         <v>3</v>
       </c>
-      <c r="Y27" t="n">
-        <v>4</v>
-      </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>2</v>
       </c>
       <c r="X30" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="Y30" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK30" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5872,14 +5872,14 @@
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6264,10 +6264,10 @@
         <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>6</v>
       </c>
       <c r="X48" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y48" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AA48" t="n">
